--- a/data/gravel/Mason Exposure 2025.xlsx
+++ b/data/gravel/Mason Exposure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CC35A2-F28B-324A-BC04-2B64CB749906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC5BB4C-7F7B-8E40-A94E-652BE3B1DC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1960" yWindow="500" windowWidth="20420" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -263,9 +263,6 @@
     <t>Mason</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>48CM</t>
   </si>
   <si>
@@ -453,6 +450,9 @@
   </si>
   <si>
     <t>rear_axle_spec</t>
+  </si>
+  <si>
+    <t>GBP</t>
   </si>
 </sst>
 </file>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -872,7 +872,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -880,7 +880,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -896,31 +896,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -933,10 +933,10 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="6">
         <v>480</v>
@@ -977,7 +977,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="6">
         <v>432.3</v>
@@ -1018,7 +1018,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="6">
         <v>77</v>
@@ -1059,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="6">
         <v>435</v>
@@ -1100,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="6">
         <v>515.9</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="6">
         <v>497.8</v>
@@ -1182,7 +1182,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" s="6">
         <v>536.1</v>
@@ -1223,7 +1223,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="6">
         <v>359.9</v>
@@ -1264,7 +1264,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="6">
         <v>721</v>
@@ -1305,7 +1305,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="6">
         <v>50</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" s="6">
         <v>74.7</v>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="6">
         <v>74.7</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6">
@@ -1503,10 +1503,10 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C23" s="6">
         <v>77.099999999999994</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6">
@@ -1586,7 +1586,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="6">
         <v>398</v>
@@ -1627,7 +1627,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="6">
         <v>69.5</v>
@@ -1668,7 +1668,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="6">
         <v>100</v>
@@ -1709,7 +1709,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="6">
         <v>74</v>
@@ -1750,7 +1750,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="6">
         <v>1013</v>
@@ -1791,7 +1791,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="6">
         <v>40</v>
@@ -1832,7 +1832,7 @@
         <v>73</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="6">
         <v>590</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="6">
         <v>142</v>
@@ -1914,7 +1914,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="6">
         <v>515</v>
@@ -1964,7 +1964,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C35" s="6">
         <v>70</v>
@@ -1996,7 +1996,7 @@
         <v>17</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C36" s="6">
         <v>165</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43">
@@ -2284,31 +2284,31 @@
         <v>67</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="E46" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="G46" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="I46" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="J46" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J46" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="K46" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
@@ -2348,7 +2348,7 @@
         <v>31</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -2592,7 +2592,7 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -2861,7 +2861,7 @@
         <v>65</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>

--- a/data/gravel/Mason Exposure 2025.xlsx
+++ b/data/gravel/Mason Exposure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC5BB4C-7F7B-8E40-A94E-652BE3B1DC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7D3B0C-F404-E847-9C28-02DC74953958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1960" yWindow="500" windowWidth="20420" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="141">
   <si>
     <t>brand</t>
   </si>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>GBP</t>
+  </si>
+  <si>
+    <t>https://masoncycles.cc/images/000/009/602/large/Exposure_Shimano_GRX1x12spd_OG_Side_Web.jpg?1746546507</t>
   </si>
 </sst>
 </file>
@@ -875,6 +878,11 @@
         <v>122</v>
       </c>
     </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Mason Exposure 2025.xlsx
+++ b/data/gravel/Mason Exposure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7D3B0C-F404-E847-9C28-02DC74953958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D93D6E3-258F-2444-B0C4-A32289DF29CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1960" yWindow="500" windowWidth="20420" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
   <si>
     <t>brand</t>
   </si>
@@ -456,6 +456,12 @@
   </si>
   <si>
     <t>https://masoncycles.cc/images/000/009/602/large/Exposure_Shimano_GRX1x12spd_OG_Side_Web.jpg?1746546507</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lancing, West Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -832,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2878,6 +2884,14 @@
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>141</v>
+      </c>
+      <c r="B84" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/data/gravel/Mason Exposure 2025.xlsx
+++ b/data/gravel/Mason Exposure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D93D6E3-258F-2444-B0C4-A32289DF29CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078D5187-7006-4D4A-9247-F5533164F730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1960" yWindow="500" windowWidth="20420" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="149">
   <si>
     <t>brand</t>
   </si>
@@ -462,6 +462,24 @@
   </si>
   <si>
     <t>Lancing, West Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -838,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2525,11 +2543,9 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2541,7 +2557,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2555,11 +2571,9 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="1">
-        <v>27.2</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -2571,11 +2585,9 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2587,11 +2599,9 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B64" s="1">
-        <v>40</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2603,11 +2613,9 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2619,10 +2627,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B66" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -2635,11 +2643,9 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B67" s="1">
-        <v>160</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2651,9 +2657,11 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B68" s="1">
+        <v>27.2</v>
+      </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -2665,9 +2673,11 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2679,9 +2689,11 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B70" s="1">
+        <v>40</v>
+      </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2693,9 +2705,11 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2707,9 +2721,11 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B72" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B72" s="1">
+        <v>180</v>
+      </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2721,10 +2737,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B73" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -2737,11 +2753,9 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B74" s="1">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -2753,11 +2767,9 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -2769,11 +2781,9 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B76" s="1">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -2781,14 +2791,13 @@
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -2796,14 +2805,13 @@
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -2811,13 +2819,14 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B79" s="1">
+        <v>2</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -2826,13 +2835,14 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B80" s="1">
-        <v>2150</v>
+        <v>1</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -2841,13 +2851,14 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81" s="1">
-        <v>3750</v>
+        <v>57</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -2856,12 +2867,15 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B82" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B82" s="1">
+        <v>3</v>
+      </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -2870,12 +2884,12 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -2885,11 +2899,99 @@
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" s="1">
+        <v>2150</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B87" s="1">
+        <v>3750</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>141</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B90" t="s">
         <v>142</v>
       </c>
     </row>
